--- a/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Claude4.5SonnetAutoGrading.xlsx
+++ b/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Claude4.5SonnetAutoGrading.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="16180" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="16180" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermonix" sheetId="1" state="visible" r:id="rId1"/>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.5</t>
+          <t>Claude</t>
         </is>
       </c>
     </row>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J8" s="70" t="inlineStr">
         <is>
-          <t>Gemini 3 Pro</t>
+          <t>Gemini</t>
         </is>
       </c>
     </row>
@@ -11187,11 +11187,7 @@
         <f>IFERROR(2*((F9*G9)/(F9+G9)),"Not Available")</f>
         <v/>
       </c>
-      <c r="J9" s="70" t="inlineStr">
-        <is>
-          <t>Claude Sonnet 4.5</t>
-        </is>
-      </c>
+      <c r="J9" s="70" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="65">
       <c r="A10" s="32" t="inlineStr">
@@ -11230,333 +11226,97 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" s="65"/>
     <row r="12" ht="15.75" customHeight="1" s="65">
-      <c r="A12" s="66" t="inlineStr">
-        <is>
-          <t>Generated by Claude Sonnet 4.5</t>
-        </is>
-      </c>
+      <c r="A12" s="66" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="65">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>Ground Truth Count</t>
-        </is>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>True Positive</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
-        <is>
-          <t>False Positive</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>False Negative</t>
-        </is>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="G13" s="28" t="inlineStr">
-        <is>
-          <t>Recall</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>F1 Score</t>
-        </is>
-      </c>
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="65">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>Composite state</t>
-        </is>
-      </c>
-      <c r="B14" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A14)</f>
-        <v/>
-      </c>
-      <c r="C14" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A14, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D14" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A14, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E14" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A14, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="31">
-        <f>IFERROR(C14 / (C14 + D14), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G14" s="31">
-        <f>IFERROR(C14 / B14, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H14" s="31">
-        <f>IFERROR(2*((F14*G14)/(F14+G14)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n"/>
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="65">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B15" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A15)</f>
-        <v/>
-      </c>
-      <c r="C15" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A15, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D15" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A15, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E15" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A15, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="31">
-        <f>IFERROR(C15 / (C15 + D15), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G15" s="31">
-        <f>IFERROR(C15 / B15, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H15" s="31">
-        <f>IFERROR(2*((F15*G15)/(F15+G15)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
+      <c r="H15" s="31" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="65">
-      <c r="A16" s="32" t="inlineStr">
-        <is>
-          <t>Transition</t>
-        </is>
-      </c>
-      <c r="B16" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A16)</f>
-        <v/>
-      </c>
-      <c r="C16" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A16, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A16, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E16" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A16, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="31">
-        <f>IFERROR(C16 / (C16 + D16), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G16" s="31">
-        <f>IFERROR(C16 / B16, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H16" s="31">
-        <f>IFERROR(2*((F16*G16)/(F16+G16)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="30" t="n"/>
+      <c r="C16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="31" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="65">
-      <c r="A17" s="32" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B17" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A17)</f>
-        <v/>
-      </c>
-      <c r="C17" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A17, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D17" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A17, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E17" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A17, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="31">
-        <f>IFERROR(C17 / (C17 + D17), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G17" s="31">
-        <f>IFERROR(C17 / B17, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H17" s="31">
-        <f>IFERROR(2*((F17*G17)/(F17+G17)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="65">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="B18" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A18)</f>
-        <v/>
-      </c>
-      <c r="C18" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A18, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D18" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A18, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E18" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A18, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="31">
-        <f>IFERROR(C18 / (C18 + D18), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G18" s="31">
-        <f>IFERROR(C18 / B18, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H18" s="31">
-        <f>IFERROR(2*((F18*G18)/(F18+G18)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="65">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>History State</t>
-        </is>
-      </c>
-      <c r="B19" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A19)</f>
-        <v/>
-      </c>
-      <c r="C19" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A19, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D19" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A19, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E19" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A19, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="31">
-        <f>IFERROR(C19 / (C19 + D19), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G19" s="31">
-        <f>IFERROR(C19 / B19, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H19" s="31">
-        <f>IFERROR(2*((F19*G19)/(F19+G19)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
+      <c r="H19" s="31" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="65">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Guard</t>
-        </is>
-      </c>
-      <c r="B20" s="30">
-        <f>COUNTIF(Thermonix!$A$2:$A$44, A20)</f>
-        <v/>
-      </c>
-      <c r="C20" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A20, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44)</f>
-        <v/>
-      </c>
-      <c r="D20" s="31">
-        <f>SUMIF('Claude Sonnet 4.5 Gen'!$A$45:$A$51, $A20, 'Claude Sonnet 4.5 Gen'!$C$45:$C$51)</f>
-        <v/>
-      </c>
-      <c r="E20" s="31">
-        <f>COUNTIFS('Claude Sonnet 4.5 Gen'!$A$2:$A$44, $A20, 'Claude Sonnet 4.5 Gen'!$C$2:$C$44,0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="31">
-        <f>IFERROR(C20 / (C20 + D20), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G20" s="31">
-        <f>IFERROR(C20 / B20, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H20" s="31">
-        <f>IFERROR(2*((F20*G20)/(F20+G20)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A20" s="32" t="n"/>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+      <c r="E20" s="31" t="n"/>
+      <c r="F20" s="31" t="n"/>
+      <c r="G20" s="31" t="n"/>
+      <c r="H20" s="31" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="65">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>Overall Score</t>
-        </is>
-      </c>
-      <c r="B21" s="31">
-        <f>SUM(B14:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="31">
-        <f>SUM(C14:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="31">
-        <f>SUM(D14:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="31">
-        <f>SUM(E14:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="31">
-        <f>IFERROR(C21 / (C21 + D21), "Not Available")</f>
-        <v/>
-      </c>
-      <c r="G21" s="31">
-        <f>IFERROR(C21 / B21, "Not Available")</f>
-        <v/>
-      </c>
-      <c r="H21" s="31">
-        <f>IFERROR(2*((F21*G21)/(F21+G21)),"Not Available")</f>
-        <v/>
-      </c>
+      <c r="A21" s="32" t="n"/>
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
+      <c r="H21" s="31" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="65"/>
     <row r="23" ht="15.75" customHeight="1" s="65"/>
@@ -12538,10 +12298,6 @@
     <row r="999" ht="15.75" customHeight="1" s="65"/>
     <row r="1000" ht="15.75" customHeight="1" s="65"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <tableParts count="2">
